--- a/Server/xno-backend/testoutput/test-file.xlsx
+++ b/Server/xno-backend/testoutput/test-file.xlsx
@@ -6,15 +6,138 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Call Sheet" r:id="rId3" sheetId="1"/>
+    <sheet name="Week 1 1" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t>Hello</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="42">
+  <si>
+    <t>3rd &amp; Short (1-3)</t>
+  </si>
+  <si>
+    <t>I-Formation</t>
+  </si>
+  <si>
+    <t>Counter Trey</t>
+  </si>
+  <si>
+    <t>FB Dive</t>
+  </si>
+  <si>
+    <t>Pistol</t>
+  </si>
+  <si>
+    <t>Pistol Power</t>
+  </si>
+  <si>
+    <t>Singleback</t>
+  </si>
+  <si>
+    <t>HB Toss</t>
+  </si>
+  <si>
+    <t>Iso Lead</t>
+  </si>
+  <si>
+    <t>3rd &amp; Long (7+)</t>
+  </si>
+  <si>
+    <t>Shotgun</t>
+  </si>
+  <si>
+    <t>Four Verticals</t>
+  </si>
+  <si>
+    <t>Trips Right</t>
+  </si>
+  <si>
+    <t>Trips Mesh</t>
+  </si>
+  <si>
+    <t>Trips Verticals</t>
+  </si>
+  <si>
+    <t>Dagger Concept</t>
+  </si>
+  <si>
+    <t>Trips Y Cross</t>
+  </si>
+  <si>
+    <t>High Red Zone (10-20)</t>
+  </si>
+  <si>
+    <t>Trips Smash</t>
+  </si>
+  <si>
+    <t>Pistol Read Option</t>
+  </si>
+  <si>
+    <t>Trips RPO Slant</t>
+  </si>
+  <si>
+    <t>PA Flood</t>
+  </si>
+  <si>
+    <t>Play Action Post</t>
+  </si>
+  <si>
+    <t>2nd &amp; Medium (4-6)</t>
+  </si>
+  <si>
+    <t>Mesh Concept</t>
+  </si>
+  <si>
+    <t>Stick Concept</t>
+  </si>
+  <si>
+    <t>Levels Concept</t>
+  </si>
+  <si>
+    <t>Drive Concept</t>
+  </si>
+  <si>
+    <t>Trips Levels</t>
+  </si>
+  <si>
+    <t>Goal Line (Inside 5)</t>
+  </si>
+  <si>
+    <t>QB Sweep</t>
+  </si>
+  <si>
+    <t>Backed Up (Inside Own 10)</t>
+  </si>
+  <si>
+    <t>Pistol Inside Zone</t>
+  </si>
+  <si>
+    <t>Singleback Dive</t>
+  </si>
+  <si>
+    <t>Inside Zone</t>
+  </si>
+  <si>
+    <t>Opening Script (First 15)</t>
+  </si>
+  <si>
+    <t>Power Right</t>
+  </si>
+  <si>
+    <t>Low Red Zone (Inside 10)</t>
+  </si>
+  <si>
+    <t>Trips HB Draw</t>
+  </si>
+  <si>
+    <t>1st &amp; 10 - Normal Field Zone</t>
+  </si>
+  <si>
+    <t>Outside Zone</t>
+  </si>
+  <si>
+    <t>Two-Minute Drill</t>
   </si>
 </sst>
 </file>
@@ -31,12 +154,112 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="darkGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="53"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="53"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="10"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="14"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="14"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="13"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="13"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="51"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="51"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="54"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="54"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="12"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="12"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="62"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="62"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="17"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="none">
+        <fgColor indexed="8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="8"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -51,23 +274,424 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="21" borderId="0" xfId="0" applyAlignment="true" applyFill="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="B1"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="11.94140625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="11.94140625" customWidth="true"/>
+    <col min="3" max="3" width="11.94140625" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="11.94140625" customWidth="true"/>
+    <col min="5" max="5" width="9.140625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="9.140625" customWidth="true"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="B1" t="s" s="0">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
+      <c r="C1" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E1" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F1" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s" s="0">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D2" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s" s="0">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>32</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="E7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>11</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="C14" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C16" s="8" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="C17" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="C18" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>4</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C23" t="s" s="0">
+        <v>6</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="C24" t="s" s="0">
+        <v>1</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>40</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E2:F2"/>
+  </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>